--- a/artfynd/A 13936-2023 artfynd.xlsx
+++ b/artfynd/A 13936-2023 artfynd.xlsx
@@ -1103,7 +1103,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113426621</v>
+        <v>113426614</v>
       </c>
       <c r="B6" t="n">
         <v>56781</v>
@@ -1143,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>296118</v>
+        <v>296101</v>
       </c>
       <c r="R6" t="n">
-        <v>6530221</v>
+        <v>6530255</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1183,7 +1183,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Färska hack</t>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1210,7 +1210,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113426614</v>
+        <v>113426621</v>
       </c>
       <c r="B7" t="n">
         <v>56781</v>
@@ -1250,10 +1250,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>296101</v>
+        <v>296118</v>
       </c>
       <c r="R7" t="n">
-        <v>6530255</v>
+        <v>6530221</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1290,7 +1290,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Hack</t>
+          <t>Färska hack</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 13936-2023 artfynd.xlsx
+++ b/artfynd/A 13936-2023 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113426617</v>
+        <v>113426616</v>
       </c>
       <c r="B2" t="n">
         <v>56781</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>296185</v>
+        <v>296106</v>
       </c>
       <c r="R2" t="n">
-        <v>6530330</v>
+        <v>6530289</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113426622</v>
+        <v>113426615</v>
       </c>
       <c r="B3" t="n">
-        <v>79169</v>
+        <v>56781</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,21 +798,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2081</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>296244</v>
+        <v>296089</v>
       </c>
       <c r="R3" t="n">
-        <v>6530306</v>
+        <v>6530262</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>På asp</t>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,7 +889,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113426615</v>
+        <v>113426617</v>
       </c>
       <c r="B4" t="n">
         <v>56781</v>
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>296089</v>
+        <v>296185</v>
       </c>
       <c r="R4" t="n">
-        <v>6530262</v>
+        <v>6530330</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -996,7 +996,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113426616</v>
+        <v>113426614</v>
       </c>
       <c r="B5" t="n">
         <v>56781</v>
@@ -1036,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>296106</v>
+        <v>296101</v>
       </c>
       <c r="R5" t="n">
-        <v>6530289</v>
+        <v>6530255</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1103,10 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113426614</v>
+        <v>113426622</v>
       </c>
       <c r="B6" t="n">
-        <v>56781</v>
+        <v>79185</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1119,21 +1119,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>2081</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1143,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>296101</v>
+        <v>296244</v>
       </c>
       <c r="R6" t="n">
-        <v>6530255</v>
+        <v>6530306</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1183,7 +1183,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Hack</t>
+          <t>På asp</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 13936-2023 artfynd.xlsx
+++ b/artfynd/A 13936-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113426616</v>
+        <v>113426622</v>
       </c>
       <c r="B2" t="n">
-        <v>56781</v>
+        <v>79185</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>2081</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>296106</v>
+        <v>296244</v>
       </c>
       <c r="R2" t="n">
-        <v>6530289</v>
+        <v>6530306</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Hack</t>
+          <t>På asp</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113426615</v>
+        <v>113426621</v>
       </c>
       <c r="B3" t="n">
         <v>56781</v>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>296089</v>
+        <v>296118</v>
       </c>
       <c r="R3" t="n">
-        <v>6530262</v>
+        <v>6530221</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Hack</t>
+          <t>Färska hack</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1103,10 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113426622</v>
+        <v>113426615</v>
       </c>
       <c r="B6" t="n">
-        <v>79185</v>
+        <v>56781</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1119,21 +1119,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2081</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1143,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>296244</v>
+        <v>296089</v>
       </c>
       <c r="R6" t="n">
-        <v>6530306</v>
+        <v>6530262</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1183,7 +1183,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>På asp</t>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1210,7 +1210,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113426621</v>
+        <v>113426616</v>
       </c>
       <c r="B7" t="n">
         <v>56781</v>
@@ -1250,10 +1250,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>296118</v>
+        <v>296106</v>
       </c>
       <c r="R7" t="n">
-        <v>6530221</v>
+        <v>6530289</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1290,7 +1290,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Färska hack</t>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 13936-2023 artfynd.xlsx
+++ b/artfynd/A 13936-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>113426622</v>
       </c>
       <c r="B2" t="n">
-        <v>79185</v>
+        <v>79197</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113426621</v>
+        <v>113426614</v>
       </c>
       <c r="B3" t="n">
-        <v>56781</v>
+        <v>56782</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>296118</v>
+        <v>296101</v>
       </c>
       <c r="R3" t="n">
-        <v>6530221</v>
+        <v>6530255</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Färska hack</t>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -892,7 +892,7 @@
         <v>113426617</v>
       </c>
       <c r="B4" t="n">
-        <v>56781</v>
+        <v>56782</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -996,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113426614</v>
+        <v>113426616</v>
       </c>
       <c r="B5" t="n">
-        <v>56781</v>
+        <v>56782</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1036,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>296101</v>
+        <v>296106</v>
       </c>
       <c r="R5" t="n">
-        <v>6530255</v>
+        <v>6530289</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1103,10 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113426615</v>
+        <v>113426621</v>
       </c>
       <c r="B6" t="n">
-        <v>56781</v>
+        <v>56782</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1143,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>296089</v>
+        <v>296118</v>
       </c>
       <c r="R6" t="n">
-        <v>6530262</v>
+        <v>6530221</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1183,7 +1183,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Hack</t>
+          <t>Färska hack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1210,10 +1210,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113426616</v>
+        <v>113426615</v>
       </c>
       <c r="B7" t="n">
-        <v>56781</v>
+        <v>56782</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1250,10 +1250,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>296106</v>
+        <v>296089</v>
       </c>
       <c r="R7" t="n">
-        <v>6530289</v>
+        <v>6530262</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>

--- a/artfynd/A 13936-2023 artfynd.xlsx
+++ b/artfynd/A 13936-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113426622</v>
+        <v>113426615</v>
       </c>
       <c r="B2" t="n">
-        <v>79197</v>
+        <v>56782</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2081</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>296244</v>
+        <v>296089</v>
       </c>
       <c r="R2" t="n">
-        <v>6530306</v>
+        <v>6530262</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>På asp</t>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -996,7 +996,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113426616</v>
+        <v>113426621</v>
       </c>
       <c r="B5" t="n">
         <v>56782</v>
@@ -1036,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>296106</v>
+        <v>296118</v>
       </c>
       <c r="R5" t="n">
-        <v>6530289</v>
+        <v>6530221</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Hack</t>
+          <t>Färska hack</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1103,7 +1103,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113426621</v>
+        <v>113426616</v>
       </c>
       <c r="B6" t="n">
         <v>56782</v>
@@ -1143,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>296118</v>
+        <v>296106</v>
       </c>
       <c r="R6" t="n">
-        <v>6530221</v>
+        <v>6530289</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1183,7 +1183,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Färska hack</t>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1210,10 +1210,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113426615</v>
+        <v>113426622</v>
       </c>
       <c r="B7" t="n">
-        <v>56782</v>
+        <v>79197</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1226,21 +1226,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>2081</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1250,10 +1250,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>296089</v>
+        <v>296244</v>
       </c>
       <c r="R7" t="n">
-        <v>6530262</v>
+        <v>6530306</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1290,7 +1290,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Hack</t>
+          <t>På asp</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 13936-2023 artfynd.xlsx
+++ b/artfynd/A 13936-2023 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113426615</v>
+        <v>113426616</v>
       </c>
       <c r="B2" t="n">
         <v>56782</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>296089</v>
+        <v>296106</v>
       </c>
       <c r="R2" t="n">
-        <v>6530262</v>
+        <v>6530289</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113426614</v>
+        <v>113426622</v>
       </c>
       <c r="B3" t="n">
-        <v>56782</v>
+        <v>79219</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,21 +798,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>2081</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>296101</v>
+        <v>296244</v>
       </c>
       <c r="R3" t="n">
-        <v>6530255</v>
+        <v>6530306</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Hack</t>
+          <t>På asp</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,7 +889,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113426617</v>
+        <v>113426621</v>
       </c>
       <c r="B4" t="n">
         <v>56782</v>
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>296185</v>
+        <v>296118</v>
       </c>
       <c r="R4" t="n">
-        <v>6530330</v>
+        <v>6530221</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -969,7 +969,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Hack</t>
+          <t>Färska hack</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,7 +996,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113426621</v>
+        <v>113426614</v>
       </c>
       <c r="B5" t="n">
         <v>56782</v>
@@ -1036,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>296118</v>
+        <v>296101</v>
       </c>
       <c r="R5" t="n">
-        <v>6530221</v>
+        <v>6530255</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Färska hack</t>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1103,7 +1103,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113426616</v>
+        <v>113426615</v>
       </c>
       <c r="B6" t="n">
         <v>56782</v>
@@ -1143,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>296106</v>
+        <v>296089</v>
       </c>
       <c r="R6" t="n">
-        <v>6530289</v>
+        <v>6530262</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1210,10 +1210,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113426622</v>
+        <v>113426617</v>
       </c>
       <c r="B7" t="n">
-        <v>79197</v>
+        <v>56782</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1226,21 +1226,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2081</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1250,10 +1250,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>296244</v>
+        <v>296185</v>
       </c>
       <c r="R7" t="n">
-        <v>6530306</v>
+        <v>6530330</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1290,7 +1290,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>På asp</t>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 13936-2023 artfynd.xlsx
+++ b/artfynd/A 13936-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113426616</v>
+        <v>113426617</v>
       </c>
       <c r="B2" t="n">
-        <v>56782</v>
+        <v>56785</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>296106</v>
+        <v>296185</v>
       </c>
       <c r="R2" t="n">
-        <v>6530289</v>
+        <v>6530330</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113426622</v>
+        <v>113426615</v>
       </c>
       <c r="B3" t="n">
-        <v>79219</v>
+        <v>56785</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,21 +798,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2081</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>296244</v>
+        <v>296089</v>
       </c>
       <c r="R3" t="n">
-        <v>6530306</v>
+        <v>6530262</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>På asp</t>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -892,7 +892,7 @@
         <v>113426621</v>
       </c>
       <c r="B4" t="n">
-        <v>56782</v>
+        <v>56785</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -996,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113426614</v>
+        <v>113426616</v>
       </c>
       <c r="B5" t="n">
-        <v>56782</v>
+        <v>56785</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1036,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>296101</v>
+        <v>296106</v>
       </c>
       <c r="R5" t="n">
-        <v>6530255</v>
+        <v>6530289</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1103,10 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113426615</v>
+        <v>113426614</v>
       </c>
       <c r="B6" t="n">
-        <v>56782</v>
+        <v>56785</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1143,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>296089</v>
+        <v>296101</v>
       </c>
       <c r="R6" t="n">
-        <v>6530262</v>
+        <v>6530255</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1210,10 +1210,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113426617</v>
+        <v>113426622</v>
       </c>
       <c r="B7" t="n">
-        <v>56782</v>
+        <v>79223</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1226,21 +1226,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>2081</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1250,10 +1250,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>296185</v>
+        <v>296244</v>
       </c>
       <c r="R7" t="n">
-        <v>6530330</v>
+        <v>6530306</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1290,7 +1290,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Hack</t>
+          <t>På asp</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 13936-2023 artfynd.xlsx
+++ b/artfynd/A 13936-2023 artfynd.xlsx
@@ -1103,10 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113426614</v>
+        <v>113426622</v>
       </c>
       <c r="B6" t="n">
-        <v>56785</v>
+        <v>79223</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1119,21 +1119,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>2081</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1143,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>296101</v>
+        <v>296244</v>
       </c>
       <c r="R6" t="n">
-        <v>6530255</v>
+        <v>6530306</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1183,7 +1183,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Hack</t>
+          <t>På asp</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1210,10 +1210,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113426622</v>
+        <v>113426614</v>
       </c>
       <c r="B7" t="n">
-        <v>79223</v>
+        <v>56785</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1226,21 +1226,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2081</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1250,10 +1250,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>296244</v>
+        <v>296101</v>
       </c>
       <c r="R7" t="n">
-        <v>6530306</v>
+        <v>6530255</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1290,7 +1290,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>På asp</t>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 13936-2023 artfynd.xlsx
+++ b/artfynd/A 13936-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113426617</v>
+        <v>113426622</v>
       </c>
       <c r="B2" t="n">
-        <v>56785</v>
+        <v>79223</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>2081</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>296185</v>
+        <v>296244</v>
       </c>
       <c r="R2" t="n">
-        <v>6530330</v>
+        <v>6530306</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Hack</t>
+          <t>På asp</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113426615</v>
+        <v>113426614</v>
       </c>
       <c r="B3" t="n">
         <v>56785</v>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>296089</v>
+        <v>296101</v>
       </c>
       <c r="R3" t="n">
-        <v>6530262</v>
+        <v>6530255</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -889,7 +889,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113426621</v>
+        <v>113426615</v>
       </c>
       <c r="B4" t="n">
         <v>56785</v>
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>296118</v>
+        <v>296089</v>
       </c>
       <c r="R4" t="n">
-        <v>6530221</v>
+        <v>6530262</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -969,7 +969,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Färska hack</t>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,7 +996,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113426616</v>
+        <v>113426617</v>
       </c>
       <c r="B5" t="n">
         <v>56785</v>
@@ -1036,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>296106</v>
+        <v>296185</v>
       </c>
       <c r="R5" t="n">
-        <v>6530289</v>
+        <v>6530330</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1103,10 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113426622</v>
+        <v>113426621</v>
       </c>
       <c r="B6" t="n">
-        <v>79223</v>
+        <v>56785</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1119,21 +1119,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2081</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1143,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>296244</v>
+        <v>296118</v>
       </c>
       <c r="R6" t="n">
-        <v>6530306</v>
+        <v>6530221</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1183,7 +1183,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>På asp</t>
+          <t>Färska hack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1210,7 +1210,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113426614</v>
+        <v>113426616</v>
       </c>
       <c r="B7" t="n">
         <v>56785</v>
@@ -1250,10 +1250,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>296101</v>
+        <v>296106</v>
       </c>
       <c r="R7" t="n">
-        <v>6530255</v>
+        <v>6530289</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>

--- a/artfynd/A 13936-2023 artfynd.xlsx
+++ b/artfynd/A 13936-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113426622</v>
+        <v>113426621</v>
       </c>
       <c r="B2" t="n">
-        <v>79223</v>
+        <v>56789</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2081</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>296244</v>
+        <v>296118</v>
       </c>
       <c r="R2" t="n">
-        <v>6530306</v>
+        <v>6530221</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>På asp</t>
+          <t>Färska hack</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113426614</v>
+        <v>113426616</v>
       </c>
       <c r="B3" t="n">
-        <v>56785</v>
+        <v>56789</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>296101</v>
+        <v>296106</v>
       </c>
       <c r="R3" t="n">
-        <v>6530255</v>
+        <v>6530289</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -892,7 +892,7 @@
         <v>113426615</v>
       </c>
       <c r="B4" t="n">
-        <v>56785</v>
+        <v>56789</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -996,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113426617</v>
+        <v>113426622</v>
       </c>
       <c r="B5" t="n">
-        <v>56785</v>
+        <v>79229</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1012,21 +1012,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>2081</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1036,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>296185</v>
+        <v>296244</v>
       </c>
       <c r="R5" t="n">
-        <v>6530330</v>
+        <v>6530306</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Hack</t>
+          <t>På asp</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1103,10 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113426621</v>
+        <v>113426614</v>
       </c>
       <c r="B6" t="n">
-        <v>56785</v>
+        <v>56789</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1143,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>296118</v>
+        <v>296101</v>
       </c>
       <c r="R6" t="n">
-        <v>6530221</v>
+        <v>6530255</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1183,7 +1183,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Färska hack</t>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1210,10 +1210,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113426616</v>
+        <v>113426617</v>
       </c>
       <c r="B7" t="n">
-        <v>56785</v>
+        <v>56789</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1250,10 +1250,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>296106</v>
+        <v>296185</v>
       </c>
       <c r="R7" t="n">
-        <v>6530289</v>
+        <v>6530330</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>

--- a/artfynd/A 13936-2023 artfynd.xlsx
+++ b/artfynd/A 13936-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113426621</v>
+        <v>113426622</v>
       </c>
       <c r="B2" t="n">
-        <v>56789</v>
+        <v>79229</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>2081</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>296118</v>
+        <v>296244</v>
       </c>
       <c r="R2" t="n">
-        <v>6530221</v>
+        <v>6530306</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Färska hack</t>
+          <t>På asp</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113426616</v>
+        <v>113426615</v>
       </c>
       <c r="B3" t="n">
         <v>56789</v>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>296106</v>
+        <v>296089</v>
       </c>
       <c r="R3" t="n">
-        <v>6530289</v>
+        <v>6530262</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -889,7 +889,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113426615</v>
+        <v>113426621</v>
       </c>
       <c r="B4" t="n">
         <v>56789</v>
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>296089</v>
+        <v>296118</v>
       </c>
       <c r="R4" t="n">
-        <v>6530262</v>
+        <v>6530221</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -969,7 +969,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Hack</t>
+          <t>Färska hack</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113426622</v>
+        <v>113426614</v>
       </c>
       <c r="B5" t="n">
-        <v>79229</v>
+        <v>56789</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1012,21 +1012,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2081</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1036,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>296244</v>
+        <v>296101</v>
       </c>
       <c r="R5" t="n">
-        <v>6530306</v>
+        <v>6530255</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>På asp</t>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1103,7 +1103,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113426614</v>
+        <v>113426616</v>
       </c>
       <c r="B6" t="n">
         <v>56789</v>
@@ -1143,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>296101</v>
+        <v>296106</v>
       </c>
       <c r="R6" t="n">
-        <v>6530255</v>
+        <v>6530289</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>

--- a/artfynd/A 13936-2023 artfynd.xlsx
+++ b/artfynd/A 13936-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113426622</v>
+        <v>113426616</v>
       </c>
       <c r="B2" t="n">
-        <v>79229</v>
+        <v>56796</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2081</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>296244</v>
+        <v>296106</v>
       </c>
       <c r="R2" t="n">
-        <v>6530306</v>
+        <v>6530289</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -755,7 +755,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>På asp</t>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -785,7 +785,7 @@
         <v>113426615</v>
       </c>
       <c r="B3" t="n">
-        <v>56789</v>
+        <v>56796</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113426621</v>
+        <v>113426617</v>
       </c>
       <c r="B4" t="n">
-        <v>56789</v>
+        <v>56796</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>296118</v>
+        <v>296185</v>
       </c>
       <c r="R4" t="n">
-        <v>6530221</v>
+        <v>6530330</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -969,7 +969,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Färska hack</t>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -999,7 +999,7 @@
         <v>113426614</v>
       </c>
       <c r="B5" t="n">
-        <v>56789</v>
+        <v>56796</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1103,10 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113426616</v>
+        <v>113426621</v>
       </c>
       <c r="B6" t="n">
-        <v>56789</v>
+        <v>56796</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1143,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>296106</v>
+        <v>296118</v>
       </c>
       <c r="R6" t="n">
-        <v>6530289</v>
+        <v>6530221</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1183,7 +1183,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Hack</t>
+          <t>Färska hack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1210,10 +1210,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113426617</v>
+        <v>113426622</v>
       </c>
       <c r="B7" t="n">
-        <v>56789</v>
+        <v>79236</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1226,21 +1226,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>2081</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1250,10 +1250,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>296185</v>
+        <v>296244</v>
       </c>
       <c r="R7" t="n">
-        <v>6530330</v>
+        <v>6530306</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1290,7 +1290,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Hack</t>
+          <t>På asp</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 13936-2023 artfynd.xlsx
+++ b/artfynd/A 13936-2023 artfynd.xlsx
@@ -1213,11 +1213,11 @@
         <v>113426622</v>
       </c>
       <c r="B7" t="n">
-        <v>79236</v>
+        <v>79238</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">

--- a/artfynd/A 13936-2023 artfynd.xlsx
+++ b/artfynd/A 13936-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113426616</v>
+        <v>113426615</v>
       </c>
       <c r="B2" t="n">
-        <v>56796</v>
+        <v>56798</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>296106</v>
+        <v>296089</v>
       </c>
       <c r="R2" t="n">
-        <v>6530289</v>
+        <v>6530262</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113426615</v>
+        <v>113426614</v>
       </c>
       <c r="B3" t="n">
-        <v>56796</v>
+        <v>56798</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>296089</v>
+        <v>296101</v>
       </c>
       <c r="R3" t="n">
-        <v>6530262</v>
+        <v>6530255</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -892,7 +892,7 @@
         <v>113426617</v>
       </c>
       <c r="B4" t="n">
-        <v>56796</v>
+        <v>56798</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -996,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113426614</v>
+        <v>113426616</v>
       </c>
       <c r="B5" t="n">
-        <v>56796</v>
+        <v>56798</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1036,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>296101</v>
+        <v>296106</v>
       </c>
       <c r="R5" t="n">
-        <v>6530255</v>
+        <v>6530289</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1106,7 +1106,7 @@
         <v>113426621</v>
       </c>
       <c r="B6" t="n">
-        <v>56796</v>
+        <v>56798</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>

--- a/artfynd/A 13936-2023 artfynd.xlsx
+++ b/artfynd/A 13936-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113426615</v>
+        <v>113426616</v>
       </c>
       <c r="B2" t="n">
-        <v>56798</v>
+        <v>56826</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>296089</v>
+        <v>296106</v>
       </c>
       <c r="R2" t="n">
-        <v>6530262</v>
+        <v>6530289</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113426614</v>
+        <v>113426617</v>
       </c>
       <c r="B3" t="n">
-        <v>56798</v>
+        <v>56826</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>296101</v>
+        <v>296185</v>
       </c>
       <c r="R3" t="n">
-        <v>6530255</v>
+        <v>6530330</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113426617</v>
+        <v>113426621</v>
       </c>
       <c r="B4" t="n">
-        <v>56798</v>
+        <v>56826</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>296185</v>
+        <v>296118</v>
       </c>
       <c r="R4" t="n">
-        <v>6530330</v>
+        <v>6530221</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -969,7 +969,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Hack</t>
+          <t>Färska hack</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113426616</v>
+        <v>113426614</v>
       </c>
       <c r="B5" t="n">
-        <v>56798</v>
+        <v>56826</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1036,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>296106</v>
+        <v>296101</v>
       </c>
       <c r="R5" t="n">
-        <v>6530289</v>
+        <v>6530255</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1103,10 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113426621</v>
+        <v>113426615</v>
       </c>
       <c r="B6" t="n">
-        <v>56798</v>
+        <v>56826</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1143,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>296118</v>
+        <v>296089</v>
       </c>
       <c r="R6" t="n">
-        <v>6530221</v>
+        <v>6530262</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1183,7 +1183,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Färska hack</t>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1213,7 +1213,7 @@
         <v>113426622</v>
       </c>
       <c r="B7" t="n">
-        <v>79238</v>
+        <v>79266</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>

--- a/artfynd/A 13936-2023 artfynd.xlsx
+++ b/artfynd/A 13936-2023 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113426616</v>
+        <v>113426615</v>
       </c>
       <c r="B2" t="n">
         <v>56826</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>296106</v>
+        <v>296089</v>
       </c>
       <c r="R2" t="n">
-        <v>6530289</v>
+        <v>6530262</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -889,7 +889,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113426621</v>
+        <v>113426616</v>
       </c>
       <c r="B4" t="n">
         <v>56826</v>
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>296118</v>
+        <v>296106</v>
       </c>
       <c r="R4" t="n">
-        <v>6530221</v>
+        <v>6530289</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -969,7 +969,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Färska hack</t>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,7 +996,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113426614</v>
+        <v>113426621</v>
       </c>
       <c r="B5" t="n">
         <v>56826</v>
@@ -1036,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>296101</v>
+        <v>296118</v>
       </c>
       <c r="R5" t="n">
-        <v>6530255</v>
+        <v>6530221</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Hack</t>
+          <t>Färska hack</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1103,7 +1103,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113426615</v>
+        <v>113426614</v>
       </c>
       <c r="B6" t="n">
         <v>56826</v>
@@ -1143,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>296089</v>
+        <v>296101</v>
       </c>
       <c r="R6" t="n">
-        <v>6530262</v>
+        <v>6530255</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>

--- a/artfynd/A 13936-2023 artfynd.xlsx
+++ b/artfynd/A 13936-2023 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113426615</v>
+        <v>113426616</v>
       </c>
       <c r="B2" t="n">
         <v>56826</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>296089</v>
+        <v>296106</v>
       </c>
       <c r="R2" t="n">
-        <v>6530262</v>
+        <v>6530289</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -782,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113426617</v>
+        <v>113426614</v>
       </c>
       <c r="B3" t="n">
         <v>56826</v>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>296185</v>
+        <v>296101</v>
       </c>
       <c r="R3" t="n">
-        <v>6530330</v>
+        <v>6530255</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -889,7 +889,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113426616</v>
+        <v>113426621</v>
       </c>
       <c r="B4" t="n">
         <v>56826</v>
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>296106</v>
+        <v>296118</v>
       </c>
       <c r="R4" t="n">
-        <v>6530289</v>
+        <v>6530221</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -969,7 +969,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Hack</t>
+          <t>Färska hack</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,7 +996,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113426621</v>
+        <v>113426617</v>
       </c>
       <c r="B5" t="n">
         <v>56826</v>
@@ -1036,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>296118</v>
+        <v>296185</v>
       </c>
       <c r="R5" t="n">
-        <v>6530221</v>
+        <v>6530330</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Färska hack</t>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1103,7 +1103,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113426614</v>
+        <v>113426615</v>
       </c>
       <c r="B6" t="n">
         <v>56826</v>
@@ -1143,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>296101</v>
+        <v>296089</v>
       </c>
       <c r="R6" t="n">
-        <v>6530255</v>
+        <v>6530262</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>

--- a/artfynd/A 13936-2023 artfynd.xlsx
+++ b/artfynd/A 13936-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
